--- a/checklist_forms/043_property_inquiry_form--checklist_forms.xlsx
+++ b/checklist_forms/043_property_inquiry_form--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Year Built</t>
+          <t>Year Built Range Label</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>contact_method_label</t>
+          <t>contact_method_label_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Contact Method</t>
+          <t>Contact Method Label 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>contact_number_label</t>
+          <t>contact_number_label_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Contact Number</t>
+          <t>Contact Number Label 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>contact_name_label</t>
+          <t>contact_name_label_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Contact Name</t>
+          <t>Contact Name Label 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>contact_email_label</t>
+          <t>contact_email_label_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Contact Email</t>
+          <t>Contact Email Label 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>contact_note_label</t>
+          <t>contact_note_label_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Contact Note</t>
+          <t>Contact Note Label 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>property_label</t>
+          <t>property_label_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Property</t>
+          <t>Property Label 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>price_label</t>
+          <t>price_label_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>Price Label 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>price_range_label</t>
+          <t>price_range_label_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Price Range</t>
+          <t>Price Range Label 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sqft_label</t>
+          <t>sqft_label_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sq Ft</t>
+          <t>Sqft Label 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>contact_method_label_choices</t>
+          <t>contact_method_label_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>contact_method_label_choices</t>
+          <t>contact_method_label_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>contact_method_label_choices</t>
+          <t>contact_method_label_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1432,7 +1432,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>property_label_choices</t>
+          <t>property_label_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1449,7 +1449,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>property_label_choices</t>
+          <t>property_label_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1466,7 +1466,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>property_label_choices</t>
+          <t>property_label_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>price_range_label_choices</t>
+          <t>price_range_label_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1500,7 +1500,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>price_range_label_choices</t>
+          <t>price_range_label_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1517,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>price_range_label_choices</t>
+          <t>price_range_label_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>price_range_label_choices</t>
+          <t>price_range_label_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
